--- a/jpcore-r4/feature/medication_example_line_cs/ValueSet-jp-medication-example-line-vs.xlsx
+++ b/jpcore-r4/feature/medication_example_line_cs/ValueSet-jp-medication-example-line-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/Examples/ValueSet/JP_MedicationRequestDosageInstructionLine_VS</t>
+    <t>http://jpfhir.jp/fhir/Examples/ValueSet/JP_DosageInstructionLine_VS</t>
   </si>
   <si>
     <t>Version</t>
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/Examples/CodeSystem/JP_MedicationRequestDosageInstructionLine_CS</t>
+    <t>http://jpfhir.jp/fhir/Examples/CodeSystem/JP_DosageInstructionLine_CS</t>
   </si>
 </sst>
 </file>
